--- a/staging-site/sites/insurance/public/underwriting-latest.xlsx
+++ b/staging-site/sites/insurance/public/underwriting-latest.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="451">
   <si>
     <t>BASTION AI-AGENT CYBER SELF-ASSESSMENT</t>
   </si>
@@ -45,1239 +45,1236 @@
     <t>Last modified</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Acme Logistics</t>
+  </si>
+  <si>
+    <t>Client industry</t>
+  </si>
+  <si>
+    <t>Last-Mile Logistics</t>
+  </si>
+  <si>
+    <t>Assessor</t>
+  </si>
+  <si>
+    <t>Bastion Security</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>Continuous AI-Agent Telemetry + Semantic NLI (gpt-4o) + Hand-curated Policy Vault (SurrealDB)</t>
+  </si>
+  <si>
+    <t>Frameworks aligned</t>
+  </si>
+  <si>
+    <t>NIST AI RMF 1.0 · ISO/IEC 42001:2023 · OWASP LLM Top 10 · EU AI Act · MITRE ATLAS</t>
+  </si>
+  <si>
+    <t>Section Index</t>
+  </si>
+  <si>
+    <t>1. Summary</t>
+  </si>
+  <si>
+    <t>Standard cyber control (Marsh-aligned)</t>
+  </si>
+  <si>
+    <t>2. Fleet</t>
+  </si>
+  <si>
+    <t>3. Risk Model</t>
+  </si>
+  <si>
+    <t>Bastion-specific (AI-native control)</t>
+  </si>
+  <si>
+    <t>4. Findings</t>
+  </si>
+  <si>
+    <t>5. Incidents</t>
+  </si>
+  <si>
+    <t>6. Telemetry</t>
+  </si>
+  <si>
+    <t>7. Framework Map</t>
+  </si>
+  <si>
+    <t>8. Attestation</t>
+  </si>
+  <si>
+    <t>1. SUMMARY</t>
+  </si>
+  <si>
+    <t>Sr.No</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Available Option</t>
+  </si>
+  <si>
+    <t>Company Response</t>
+  </si>
+  <si>
+    <t>1.1 — Headline Metrics</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Benchmark (industry p50)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Fleet risk score (net, with Bastion)</t>
+  </si>
+  <si>
+    <t>20.0 / 100</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Fleet risk score (gross, without controls)</t>
+  </si>
+  <si>
+    <t>69.9 / 100</t>
+  </si>
+  <si>
+    <t>70.5</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Risk reduction attributable to Bastion</t>
+  </si>
+  <si>
+    <t>-71.4%</t>
+  </si>
+  <si>
+    <t>-28.0%</t>
+  </si>
+  <si>
+    <t>Outperforming</t>
+  </si>
+  <si>
+    <t>Agents monitored</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Total transactions (reporting period)</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Monitoring hours</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>Total incidents (30d)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Critical incidents (30d)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PII remediation rate</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>78.2%</t>
+  </si>
+  <si>
+    <t>Actions blocked (policy violations)</t>
+  </si>
+  <si>
+    <t>2 of 36</t>
+  </si>
+  <si>
+    <t>14 of 100</t>
+  </si>
+  <si>
+    <t>On target</t>
+  </si>
+  <si>
+    <t>Anomaly rate</t>
+  </si>
+  <si>
+    <t>4.88%</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>Avg latency (NLI gated egress)</t>
+  </si>
+  <si>
+    <t>1.3s</t>
+  </si>
+  <si>
+    <t>API spend (6mo)</t>
+  </si>
+  <si>
+    <t>$0.38</t>
+  </si>
+  <si>
+    <t>1.2 — Classification</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Risk classification</t>
+  </si>
+  <si>
+    <t>Low Risk</t>
+  </si>
+  <si>
+    <t>Controls credit observed</t>
+  </si>
+  <si>
+    <t>-71.4% (delta between gross and net risk score)</t>
+  </si>
+  <si>
+    <t>Next review</t>
+  </si>
+  <si>
+    <t>2026-07-24 (quarterly)</t>
+  </si>
+  <si>
+    <t>2. FLEET</t>
+  </si>
+  <si>
+    <t>2.1 — Per-Agent Metrics (reporting period)</t>
+  </si>
+  <si>
+    <t>6 customer-facing or back-office AI agents. Each agent has its own permissions and rule set, enforced before every reply is sent.</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Cost ($)</t>
+  </si>
+  <si>
+    <t>Avg Latency</t>
+  </si>
+  <si>
+    <t>PII Flags</t>
+  </si>
+  <si>
+    <t>Tool Blocks</t>
+  </si>
+  <si>
+    <t>Risk %</t>
+  </si>
+  <si>
+    <t>Acme Phone AI</t>
+  </si>
+  <si>
+    <t>Voice inbound</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>$0.04</t>
+  </si>
+  <si>
+    <t>0.8s</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>19.5%</t>
+  </si>
+  <si>
+    <t>Hub Coordinator</t>
+  </si>
+  <si>
+    <t>Internal API</t>
+  </si>
+  <si>
+    <t>$0.12</t>
+  </si>
+  <si>
+    <t>1.9s</t>
+  </si>
+  <si>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Driver Dispatch</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>$0.09</t>
+  </si>
+  <si>
+    <t>1.4s</t>
+  </si>
+  <si>
+    <t>Billing Assistant</t>
+  </si>
+  <si>
+    <t>Chat + API</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>$0.07</t>
+  </si>
+  <si>
+    <t>1.2s</t>
+  </si>
+  <si>
+    <t>Safety Coordinator</t>
+  </si>
+  <si>
+    <t>Phone + chat</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>$0.02</t>
+  </si>
+  <si>
+    <t>0.7s</t>
+  </si>
+  <si>
+    <t>14.6%</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Compliance Monitor</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>$0.01</t>
+  </si>
+  <si>
+    <t>0.5s</t>
+  </si>
+  <si>
+    <t>2.2 — Tool Authority Boundaries</t>
+  </si>
+  <si>
+    <t>Allowed Tools</t>
+  </si>
+  <si>
+    <t>Restricted Tools (KG-enforced)</t>
+  </si>
+  <si>
+    <t>tracking_lookup, billing_lookup, create_ticket, escalate_supervisor</t>
+  </si>
+  <si>
+    <t>dispatch_911, driver_reroute, refund_over_100</t>
+  </si>
+  <si>
+    <t>hub_status, sortation_metrics, shift_roster</t>
+  </si>
+  <si>
+    <t>driver_comms, refund_issue</t>
+  </si>
+  <si>
+    <t>driver_roster, reroute_parcel, weather_feed</t>
+  </si>
+  <si>
+    <t>billing_adjustment, compliance_override</t>
+  </si>
+  <si>
+    <t>invoice_query, apply_credit_up_to_100, refund_request</t>
+  </si>
+  <si>
+    <t>dispatch_driver, hub_shift_change</t>
+  </si>
+  <si>
+    <t>dispatch_911, hazmat_protocol, driver_status</t>
+  </si>
+  <si>
+    <t>billing_adjustment, shift_change</t>
+  </si>
+  <si>
+    <t>audit_log_query, hos_compliance_check, incident_report</t>
+  </si>
+  <si>
+    <t>refund_issue, driver_reroute</t>
+  </si>
+  <si>
+    <t>3. RISK MODEL   ·   BASTION-SPECIFIC</t>
+  </si>
+  <si>
+    <t>3.1 — Gross / Net / Reduction</t>
+  </si>
+  <si>
+    <t>Gross = fleet risk score if agents ran without Bastion. Net = same fleet with Bastion controls inline. Reduction is the insurer's applied-controls credit.</t>
+  </si>
+  <si>
+    <t>Posture</t>
+  </si>
+  <si>
+    <t>Risk Score</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Eligible For</t>
+  </si>
+  <si>
+    <t>Without controls (gross)</t>
+  </si>
+  <si>
+    <t>69.9</t>
+  </si>
+  <si>
+    <t>Enhanced tier, surcharged</t>
+  </si>
+  <si>
+    <t>With Bastion Blue (net)</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>Standard tier, baseline pricing</t>
+  </si>
+  <si>
+    <t>Reduction</t>
+  </si>
+  <si>
+    <t>3.2 — Score Decomposition</t>
+  </si>
+  <si>
+    <t>Weighted components. Full methodology in sheet 8.</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Benchmark (p50)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>PII exposure</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>78.2</t>
+  </si>
+  <si>
+    <t>Rate of unredacted PII in agent outputs</t>
+  </si>
+  <si>
+    <t>Policy violations</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>79.6</t>
+  </si>
+  <si>
+    <t>62.5</t>
+  </si>
+  <si>
+    <t>Tool calls that violated enforcement boundaries</t>
+  </si>
+  <si>
+    <t>Behavioral anomaly</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>81.0</t>
+  </si>
+  <si>
+    <t>Statistical deviation from baseline</t>
+  </si>
+  <si>
+    <t>Output integrity</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>94.3</t>
+  </si>
+  <si>
+    <t>70.1</t>
+  </si>
+  <si>
+    <t>Hallucinated data / unverifiable claims</t>
+  </si>
+  <si>
+    <t>Model drift</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>98.1</t>
+  </si>
+  <si>
+    <t>83.4</t>
+  </si>
+  <si>
+    <t>Systematic output-distribution change</t>
+  </si>
+  <si>
+    <t>3.3 — Risk Contribution by Line Item</t>
+  </si>
+  <si>
+    <t>Per-line-item risk-score contribution. Gross = score contribution without Bastion controls in place. Net = residual contribution after Bastion enforcement during the assessment period. Reduction = applied-controls credit per line item.</t>
+  </si>
+  <si>
+    <t>Line Item</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Per-Event Weight</t>
+  </si>
+  <si>
+    <t>Gross</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Net</t>
+  </si>
+  <si>
+    <t>PII records (detected)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Tool-violation attempts</t>
+  </si>
+  <si>
+    <t>12.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>Session rollback (ops)</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Total risk contribution</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>41.5</t>
+  </si>
+  <si>
+    <t>Reduction (delta)</t>
+  </si>
+  <si>
+    <t>-40.0</t>
+  </si>
+  <si>
+    <t>4. FINDINGS   ·   BASTION-SPECIFIC</t>
+  </si>
+  <si>
+    <t>4.1 — Live Detections (last 30 days)</t>
+  </si>
+  <si>
+    <t>Every finding comes from Bastion's combined AI groundedness, knowledge-base, and authorization checks, and is tagged with the relevant compliance framework. Updated live every 4 seconds.</t>
+  </si>
+  <si>
+    <t>Finding ID</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Detection</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Framework Tags</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-23-001</t>
+  </si>
+  <si>
+    <t>2026-04-23 14:22</t>
+  </si>
+  <si>
+    <t>acme_phone_ai</t>
+  </si>
+  <si>
+    <t>canary_disclosure</t>
+  </si>
+  <si>
+    <t>Blocked inline</t>
+  </si>
+  <si>
+    <t>AI-RMF:MEASURE-2.7 · OWASP:LLM01 · ISO-42001:A.6.2.7 · ATLAS:AML.T0054</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-23-002</t>
+  </si>
+  <si>
+    <t>2026-04-23 16:08</t>
+  </si>
+  <si>
+    <t>policy_violation</t>
+  </si>
+  <si>
+    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM08 · EU-AI:Art.14</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-22-017</t>
+  </si>
+  <si>
+    <t>2026-04-22 19:55</t>
+  </si>
+  <si>
+    <t>billing_assistant</t>
+  </si>
+  <si>
+    <t>third_party_disclosure</t>
+  </si>
+  <si>
+    <t>Flagged for review</t>
+  </si>
+  <si>
+    <t>AI-RMF:MEASURE-2.10 · OWASP:LLM06 · EU-AI:Art.10</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-21-004</t>
+  </si>
+  <si>
+    <t>2026-04-21 09:12</t>
+  </si>
+  <si>
+    <t>divergence</t>
+  </si>
+  <si>
+    <t>Remediated (prompt patch)</t>
+  </si>
+  <si>
+    <t>AI-RMF:MEASURE-2.3 · OWASP:LLM09</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-19-022</t>
+  </si>
+  <si>
+    <t>2026-04-19 13:40</t>
+  </si>
+  <si>
+    <t>safety_coordinator</t>
+  </si>
+  <si>
+    <t>pii_leak</t>
+  </si>
+  <si>
+    <t>AI-RMF:MEASURE-2.10 · OWASP:LLM06</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-18-008</t>
+  </si>
+  <si>
+    <t>2026-04-18 11:03</t>
+  </si>
+  <si>
+    <t>AI-RMF:MEASURE-2.7 · OWASP:LLM01 · ATLAS:AML.T0054</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-04-17-031</t>
+  </si>
+  <si>
+    <t>2026-04-17 22:14</t>
+  </si>
+  <si>
+    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM08</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-05-16-011</t>
+  </si>
+  <si>
+    <t>2026-05-16 10:28</t>
+  </si>
+  <si>
+    <t>BSTN-F-2026-05-14-047</t>
+  </si>
+  <si>
+    <t>2026-05-14 15:51</t>
+  </si>
+  <si>
+    <t>Remediated</t>
+  </si>
+  <si>
+    <t>4.2 — Detection Class Breakdown (30d)</t>
+  </si>
+  <si>
+    <t>Detection Class</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Blocked Inline %</t>
+  </si>
+  <si>
+    <t>Remediated %</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>5. INCIDENTS</t>
+  </si>
+  <si>
+    <t>5.1 — Incident Register (last 12 months)</t>
+  </si>
+  <si>
+    <t>Curated from runner registry + manual incident reports. An "incident" = a finding escalated to AI Officer review or higher.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>Prompt injection (jailbreak attempt)</t>
+  </si>
+  <si>
+    <t>Blocked inline. No disclosure.</t>
+  </si>
+  <si>
+    <t>None required</t>
+  </si>
+  <si>
+    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM01</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>Third-party PII disclosure (partial)</t>
+  </si>
+  <si>
+    <t>Caught at NLI egress. 0 records released.</t>
+  </si>
+  <si>
+    <t>Internal AI Officer</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>Hallucinated delivery date</t>
+  </si>
+  <si>
+    <t>Flagged by divergence check. Caller notified of error.</t>
+  </si>
+  <si>
+    <t>5.2 — Severity Distribution</t>
+  </si>
+  <si>
+    <t>Severity Level</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Avg Risk Weight</t>
+  </si>
+  <si>
+    <t>SEV-1 Critical</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>SEV-2 Major</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>SEV-3 Moderate</t>
+  </si>
+  <si>
+    <t>44.4%</t>
+  </si>
+  <si>
+    <t>SEV-4 Minor</t>
+  </si>
+  <si>
+    <t>33.3%</t>
+  </si>
+  <si>
+    <t>SEV-5 Info</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>6. TELEMETRY   ·   BASTION-SPECIFIC</t>
+  </si>
+  <si>
+    <t>6.1 — PII Metrics</t>
+  </si>
+  <si>
+    <t>PII Type</t>
+  </si>
+  <si>
+    <t>Detected</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Per-Record Risk Weight</t>
+  </si>
+  <si>
+    <t>Residual Risk</t>
+  </si>
+  <si>
+    <t>Phone number</t>
+  </si>
+  <si>
+    <t>Physical address</t>
+  </si>
+  <si>
+    <t>Named person (third-party)</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>SSN / SIN</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>Credit card</t>
+  </si>
+  <si>
+    <t>6.2 — Tool Call Metrics</t>
+  </si>
+  <si>
+    <t>Total tool calls attempted</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Blocked by policy</t>
+  </si>
+  <si>
+    <t>Block rate</t>
+  </si>
+  <si>
+    <t>5.56%</t>
+  </si>
+  <si>
+    <t>Top blocked category</t>
+  </si>
+  <si>
+    <t>refund_over_supervisor_threshold</t>
+  </si>
+  <si>
+    <t>Privileged-action threshold violations</t>
+  </si>
+  <si>
+    <t>6.3 — Anomaly &amp; Drift</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>Anomaly rate (novel tool patterns)</t>
+  </si>
+  <si>
+    <t>Within bounds</t>
+  </si>
+  <si>
+    <t>Rate anomalies (burst detection)</t>
+  </si>
+  <si>
+    <t>3 / 15s</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>Novel tool alerts</t>
+  </si>
+  <si>
+    <t>5 / week</t>
+  </si>
+  <si>
+    <t>Consistency score (hallucination rate)</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>&lt; 0.8 alerts</t>
+  </si>
+  <si>
+    <t>Behavior change detection</t>
+  </si>
+  <si>
+    <t>nominal</t>
+  </si>
+  <si>
+    <t>conservative / fail-closed</t>
+  </si>
+  <si>
+    <t>Nominal</t>
+  </si>
+  <si>
+    <t>7. FRAMEWORK MAP   ·   BASTION-SPECIFIC</t>
+  </si>
+  <si>
+    <t>7.1 — Detection × Framework Matrix</t>
+  </si>
+  <si>
+    <t>Every Bastion detection type carries simultaneous tags for NIST AI RMF, OWASP LLM Top 10, ISO/IEC 42001, EU AI Act, and MITRE ATLAS. This is the matrix underwriters price against.</t>
+  </si>
+  <si>
+    <t>Bastion Detection</t>
+  </si>
+  <si>
+    <t>NIST AI RMF 1.0</t>
+  </si>
+  <si>
+    <t>OWASP LLM Top 10</t>
+  </si>
+  <si>
+    <t>ISO/IEC 42001</t>
+  </si>
+  <si>
+    <t>EU AI Act</t>
+  </si>
+  <si>
+    <t>MITRE ATLAS</t>
+  </si>
+  <si>
+    <t>MEASURE-2.10, MANAGE-4.3</t>
+  </si>
+  <si>
+    <t>LLM06</t>
+  </si>
+  <si>
+    <t>A.6.1.5, A.6.2.7</t>
+  </si>
+  <si>
+    <t>Art. 10, Art. 13</t>
+  </si>
+  <si>
+    <t>AML.T0051</t>
+  </si>
+  <si>
+    <t>MEASURE-2.10, MEASURE-2.3</t>
+  </si>
+  <si>
+    <t>A.6.1.5</t>
+  </si>
+  <si>
+    <t>Art. 10</t>
+  </si>
+  <si>
+    <t>AML.T0024</t>
+  </si>
+  <si>
+    <t>divergence (hallucination)</t>
+  </si>
+  <si>
+    <t>MEASURE-2.3, MEASURE-2.8</t>
+  </si>
+  <si>
+    <t>LLM09</t>
+  </si>
+  <si>
+    <t>A.6.2.4</t>
+  </si>
+  <si>
+    <t>Art. 15</t>
+  </si>
+  <si>
+    <t>AML.T0043</t>
+  </si>
+  <si>
+    <t>canary_disclosure (prompt / tool leak)</t>
+  </si>
+  <si>
+    <t>MEASURE-2.7, MANAGE-2.3</t>
+  </si>
+  <si>
+    <t>LLM01, LLM02</t>
+  </si>
+  <si>
+    <t>A.6.2.7, A.6.2.8</t>
+  </si>
+  <si>
+    <t>Art. 15 (cyber)</t>
+  </si>
+  <si>
+    <t>AML.T0054</t>
+  </si>
+  <si>
+    <t>policy_violation (excessive agency)</t>
+  </si>
+  <si>
+    <t>MANAGE-4.2, GOVERN-3.2</t>
+  </si>
+  <si>
+    <t>LLM08</t>
+  </si>
+  <si>
+    <t>A.6.1.2, A.6.2.1</t>
+  </si>
+  <si>
+    <t>Art. 14 (oversight)</t>
+  </si>
+  <si>
+    <t>AML.T0053</t>
+  </si>
+  <si>
+    <t>behavior change detection</t>
+  </si>
+  <si>
+    <t>MEASURE-3.2, MEASURE-4.1</t>
+  </si>
+  <si>
+    <t>A.6.2.5</t>
+  </si>
+  <si>
+    <t>Art. 15 (accuracy)</t>
+  </si>
+  <si>
+    <t>AML.T0034</t>
+  </si>
+  <si>
+    <t>red-team finding (adversarial)</t>
+  </si>
+  <si>
+    <t>MANAGE-4.1, MAP-5.1</t>
+  </si>
+  <si>
+    <t>A.6.2.6</t>
+  </si>
+  <si>
+    <t>Art. 15, Annex IV</t>
+  </si>
+  <si>
+    <t>Per-finding ATLAS ID</t>
+  </si>
+  <si>
+    <t>7.2 — Framework Coverage Summary</t>
+  </si>
+  <si>
+    <t>Framework</t>
+  </si>
+  <si>
+    <t>Controls Tagged</t>
+  </si>
+  <si>
+    <t>Coverage %</t>
+  </si>
+  <si>
+    <t>NIST AI RMF</t>
+  </si>
+  <si>
+    <t>1.0 (Jan 2023)</t>
+  </si>
+  <si>
+    <t>9 categories (GOVERN, MAP, MEASURE, MANAGE)</t>
+  </si>
+  <si>
+    <t>86%</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>10 / 10</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>9 controls in A.6.x</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>final 2024</t>
+  </si>
+  <si>
+    <t>Art. 10, 13, 14, 15 + Annex IV</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>2025.1</t>
+  </si>
+  <si>
+    <t>7 tactics / 14 techniques</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>8. ATTESTATION</t>
+  </si>
+  <si>
+    <t>8.1 — Controls In Place</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Last Verified</t>
+  </si>
+  <si>
+    <t>AI reviewer evaluates every agent reply</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Groundedness + Authorization</t>
+  </si>
+  <si>
     <t>2026-04-24</t>
   </si>
   <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Acme Logistics</t>
-  </si>
-  <si>
-    <t>Client industry</t>
-  </si>
-  <si>
-    <t>Last-Mile Logistics</t>
-  </si>
-  <si>
-    <t>Assessor</t>
-  </si>
-  <si>
-    <t>Bastion Security</t>
-  </si>
-  <si>
-    <t>Methodology</t>
-  </si>
-  <si>
-    <t>Continuous AI-Agent Telemetry + Semantic NLI (gpt-4o) + Hand-curated Policy Vault (SurrealDB)</t>
-  </si>
-  <si>
-    <t>Frameworks aligned</t>
-  </si>
-  <si>
-    <t>NIST AI RMF 1.0 · ISO/IEC 42001:2023 · OWASP LLM Top 10 · EU AI Act · MITRE ATLAS</t>
-  </si>
-  <si>
-    <t>Section Index</t>
-  </si>
-  <si>
-    <t>1. Summary</t>
-  </si>
-  <si>
-    <t>Standard cyber control (Marsh-aligned)</t>
-  </si>
-  <si>
-    <t>2. Fleet</t>
-  </si>
-  <si>
-    <t>3. Risk Model</t>
-  </si>
-  <si>
-    <t>Bastion-specific (AI-native control)</t>
-  </si>
-  <si>
-    <t>4. Findings</t>
-  </si>
-  <si>
-    <t>5. Incidents</t>
-  </si>
-  <si>
-    <t>6. Telemetry</t>
-  </si>
-  <si>
-    <t>7. Framework Map</t>
-  </si>
-  <si>
-    <t>8. Attestation</t>
-  </si>
-  <si>
-    <t>1. SUMMARY</t>
-  </si>
-  <si>
-    <t>Sr.No</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Available Option</t>
-  </si>
-  <si>
-    <t>Company Response</t>
-  </si>
-  <si>
-    <t>1.1 — Headline Metrics</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Benchmark (industry p50)</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Fleet risk score (net, with Bastion)</t>
-  </si>
-  <si>
-    <t>20.0 / 100</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Fleet risk score (gross, without controls)</t>
-  </si>
-  <si>
-    <t>69.9 / 100</t>
-  </si>
-  <si>
-    <t>70.5</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Risk reduction attributable to Bastion</t>
-  </si>
-  <si>
-    <t>-71.4%</t>
-  </si>
-  <si>
-    <t>-28.0%</t>
-  </si>
-  <si>
-    <t>Outperforming</t>
-  </si>
-  <si>
-    <t>Agents monitored</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Total transactions (reporting period)</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Monitoring hours</t>
-  </si>
-  <si>
-    <t>336</t>
-  </si>
-  <si>
-    <t>Total incidents (30d)</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Critical incidents (30d)</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PII remediation rate</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>78.2%</t>
-  </si>
-  <si>
-    <t>Actions blocked (policy violations)</t>
-  </si>
-  <si>
-    <t>2 of 36</t>
-  </si>
-  <si>
-    <t>14 of 100</t>
-  </si>
-  <si>
-    <t>On target</t>
-  </si>
-  <si>
-    <t>Anomaly rate</t>
-  </si>
-  <si>
-    <t>4.88%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>Avg latency (NLI gated egress)</t>
-  </si>
-  <si>
-    <t>1.3s</t>
-  </si>
-  <si>
-    <t>API spend (6mo)</t>
-  </si>
-  <si>
-    <t>$0.38</t>
-  </si>
-  <si>
-    <t>1.2 — Classification</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Risk classification</t>
-  </si>
-  <si>
-    <t>Low Risk</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Eligible for standard AI-liability coverage</t>
-  </si>
-  <si>
-    <t>Coverage tier suggested</t>
-  </si>
-  <si>
-    <t>Premium adjustment vs baseline</t>
-  </si>
-  <si>
-    <t>-18% (applied controls credit)</t>
-  </si>
-  <si>
-    <t>Next review</t>
-  </si>
-  <si>
-    <t>2026-07-24 (quarterly)</t>
-  </si>
-  <si>
-    <t>2. FLEET</t>
-  </si>
-  <si>
-    <t>2.1 — Per-Agent Metrics (reporting period)</t>
-  </si>
-  <si>
-    <t>6 customer-facing or back-office AI agents. Each agent has its own permissions and rule set, enforced before every reply is sent.</t>
-  </si>
-  <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>Channel</t>
-  </si>
-  <si>
-    <t>Requests</t>
-  </si>
-  <si>
-    <t>Cost ($)</t>
-  </si>
-  <si>
-    <t>Avg Latency</t>
-  </si>
-  <si>
-    <t>PII Flags</t>
-  </si>
-  <si>
-    <t>Tool Blocks</t>
-  </si>
-  <si>
-    <t>Risk %</t>
-  </si>
-  <si>
-    <t>Acme Phone AI</t>
-  </si>
-  <si>
-    <t>Voice inbound</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>$0.04</t>
-  </si>
-  <si>
-    <t>0.8s</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>19.5%</t>
-  </si>
-  <si>
-    <t>Hub Coordinator</t>
-  </si>
-  <si>
-    <t>Internal API</t>
-  </si>
-  <si>
-    <t>$0.12</t>
-  </si>
-  <si>
-    <t>1.9s</t>
-  </si>
-  <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Driver Dispatch</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>$0.09</t>
-  </si>
-  <si>
-    <t>1.4s</t>
-  </si>
-  <si>
-    <t>Billing Assistant</t>
-  </si>
-  <si>
-    <t>Chat + API</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>$0.07</t>
-  </si>
-  <si>
-    <t>1.2s</t>
-  </si>
-  <si>
-    <t>Safety Coordinator</t>
-  </si>
-  <si>
-    <t>Phone + chat</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>$0.02</t>
-  </si>
-  <si>
-    <t>0.7s</t>
-  </si>
-  <si>
-    <t>14.6%</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>Compliance Monitor</t>
-  </si>
-  <si>
-    <t>Internal</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>$0.01</t>
-  </si>
-  <si>
-    <t>0.5s</t>
-  </si>
-  <si>
-    <t>2.2 — Tool Authority Boundaries</t>
-  </si>
-  <si>
-    <t>Allowed Tools</t>
-  </si>
-  <si>
-    <t>Restricted Tools (KG-enforced)</t>
-  </si>
-  <si>
-    <t>tracking_lookup, billing_lookup, create_ticket, escalate_supervisor</t>
-  </si>
-  <si>
-    <t>dispatch_911, driver_reroute, refund_over_100</t>
-  </si>
-  <si>
-    <t>hub_status, sortation_metrics, shift_roster</t>
-  </si>
-  <si>
-    <t>driver_comms, refund_issue</t>
-  </si>
-  <si>
-    <t>driver_roster, reroute_parcel, weather_feed</t>
-  </si>
-  <si>
-    <t>billing_adjustment, compliance_override</t>
-  </si>
-  <si>
-    <t>invoice_query, apply_credit_up_to_100, refund_request</t>
-  </si>
-  <si>
-    <t>dispatch_driver, hub_shift_change</t>
-  </si>
-  <si>
-    <t>dispatch_911, hazmat_protocol, driver_status</t>
-  </si>
-  <si>
-    <t>billing_adjustment, shift_change</t>
-  </si>
-  <si>
-    <t>audit_log_query, hos_compliance_check, incident_report</t>
-  </si>
-  <si>
-    <t>refund_issue, driver_reroute</t>
-  </si>
-  <si>
-    <t>3. RISK MODEL   ·   BASTION-SPECIFIC</t>
-  </si>
-  <si>
-    <t>3.1 — Gross / Net / Reduction</t>
-  </si>
-  <si>
-    <t>Gross = fleet risk score if agents ran without Bastion. Net = same fleet with Bastion controls inline. Reduction is the insurer's applied-controls credit.</t>
-  </si>
-  <si>
-    <t>Posture</t>
-  </si>
-  <si>
-    <t>Risk Score</t>
-  </si>
-  <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Eligible For</t>
-  </si>
-  <si>
-    <t>Without controls (gross)</t>
-  </si>
-  <si>
-    <t>69.9</t>
-  </si>
-  <si>
-    <t>Enhanced tier, surcharged</t>
-  </si>
-  <si>
-    <t>With Bastion Blue (net)</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>Standard tier, baseline pricing</t>
-  </si>
-  <si>
-    <t>Reduction</t>
-  </si>
-  <si>
-    <t>3.2 — Score Decomposition</t>
-  </si>
-  <si>
-    <t>Weighted components. Full methodology in sheet 8.</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>Benchmark (p50)</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>PII exposure</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>78.2</t>
-  </si>
-  <si>
-    <t>Rate of unredacted PII in agent outputs</t>
-  </si>
-  <si>
-    <t>Policy violations</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>79.6</t>
-  </si>
-  <si>
-    <t>62.5</t>
-  </si>
-  <si>
-    <t>Tool calls that violated enforcement boundaries</t>
-  </si>
-  <si>
-    <t>Behavioral anomaly</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>81.0</t>
-  </si>
-  <si>
-    <t>Statistical deviation from baseline</t>
-  </si>
-  <si>
-    <t>Output integrity</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>94.3</t>
-  </si>
-  <si>
-    <t>70.1</t>
-  </si>
-  <si>
-    <t>Hallucinated data / unverifiable claims</t>
-  </si>
-  <si>
-    <t>Model drift</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>98.1</t>
-  </si>
-  <si>
-    <t>83.4</t>
-  </si>
-  <si>
-    <t>Systematic output-distribution change</t>
-  </si>
-  <si>
-    <t>3.3 — Financial Exposure</t>
-  </si>
-  <si>
-    <t>Per-record settlement benchmark: IBM/Ponemon 2025 $180/PII record. Gross = estimated liability without redaction. Net = residual after Bastion controls.</t>
-  </si>
-  <si>
-    <t>Line Item</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Per-Record</t>
-  </si>
-  <si>
-    <t>Gross</t>
-  </si>
-  <si>
-    <t>Residual</t>
-  </si>
-  <si>
-    <t>Net</t>
-  </si>
-  <si>
-    <t>PII records (detected)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>$180</t>
-  </si>
-  <si>
-    <t>$720</t>
-  </si>
-  <si>
-    <t>$0</t>
-  </si>
-  <si>
-    <t>Tool-violation attempts</t>
-  </si>
-  <si>
-    <t>$5,000</t>
-  </si>
-  <si>
-    <t>$10,000</t>
-  </si>
-  <si>
-    <t>Session rollback cost (ops)</t>
-  </si>
-  <si>
-    <t>$450</t>
-  </si>
-  <si>
-    <t>Total liability exposure</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>$11,170</t>
-  </si>
-  <si>
-    <t>Reduction ($)</t>
-  </si>
-  <si>
-    <t>$10,720</t>
-  </si>
-  <si>
-    <t>4. FINDINGS   ·   BASTION-SPECIFIC</t>
-  </si>
-  <si>
-    <t>4.1 — Live Detections (last 30 days)</t>
-  </si>
-  <si>
-    <t>Every finding comes from Bastion's combined AI groundedness, knowledge-base, and authorization checks, and is tagged with the relevant compliance framework. Updated live every 4 seconds.</t>
-  </si>
-  <si>
-    <t>Finding ID</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Detection</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Framework Tags</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-23-001</t>
-  </si>
-  <si>
-    <t>2026-04-23 14:22</t>
-  </si>
-  <si>
-    <t>acme_phone_ai</t>
-  </si>
-  <si>
-    <t>canary_disclosure</t>
-  </si>
-  <si>
-    <t>Blocked inline</t>
-  </si>
-  <si>
-    <t>AI-RMF:MEASURE-2.7 · OWASP:LLM01 · ISO-42001:A.6.2.7 · ATLAS:AML.T0054</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-23-002</t>
-  </si>
-  <si>
-    <t>2026-04-23 16:08</t>
-  </si>
-  <si>
-    <t>policy_violation</t>
-  </si>
-  <si>
-    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM08 · EU-AI:Art.14</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-22-017</t>
-  </si>
-  <si>
-    <t>2026-04-22 19:55</t>
-  </si>
-  <si>
-    <t>billing_assistant</t>
-  </si>
-  <si>
-    <t>third_party_disclosure</t>
-  </si>
-  <si>
-    <t>Flagged for review</t>
-  </si>
-  <si>
-    <t>AI-RMF:MEASURE-2.10 · OWASP:LLM06 · EU-AI:Art.10</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-21-004</t>
-  </si>
-  <si>
-    <t>2026-04-21 09:12</t>
-  </si>
-  <si>
-    <t>divergence</t>
-  </si>
-  <si>
-    <t>Remediated (prompt patch)</t>
-  </si>
-  <si>
-    <t>AI-RMF:MEASURE-2.3 · OWASP:LLM09</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-19-022</t>
-  </si>
-  <si>
-    <t>2026-04-19 13:40</t>
-  </si>
-  <si>
-    <t>safety_coordinator</t>
-  </si>
-  <si>
-    <t>pii_leak</t>
-  </si>
-  <si>
-    <t>AI-RMF:MEASURE-2.10 · OWASP:LLM06</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-18-008</t>
-  </si>
-  <si>
-    <t>2026-04-18 11:03</t>
-  </si>
-  <si>
-    <t>AI-RMF:MEASURE-2.7 · OWASP:LLM01 · ATLAS:AML.T0054</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-17-031</t>
-  </si>
-  <si>
-    <t>2026-04-17 22:14</t>
-  </si>
-  <si>
-    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM08</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-16-011</t>
-  </si>
-  <si>
-    <t>2026-04-16 10:28</t>
-  </si>
-  <si>
-    <t>BSTN-F-2026-04-14-047</t>
-  </si>
-  <si>
-    <t>2026-04-14 15:51</t>
-  </si>
-  <si>
-    <t>Remediated</t>
-  </si>
-  <si>
-    <t>4.2 — Detection Class Breakdown (30d)</t>
-  </si>
-  <si>
-    <t>Detection Class</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Blocked Inline %</t>
-  </si>
-  <si>
-    <t>Remediated %</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>5. INCIDENTS</t>
-  </si>
-  <si>
-    <t>5.1 — Incident Register (last 12 months)</t>
-  </si>
-  <si>
-    <t>Curated from runner registry + manual incident reports. An "incident" = a finding escalated to AI Officer review or higher.</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
-    <t>Notification</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>Prompt injection (jailbreak attempt)</t>
-  </si>
-  <si>
-    <t>Blocked inline. No disclosure.</t>
-  </si>
-  <si>
-    <t>None required</t>
-  </si>
-  <si>
-    <t>AI-RMF:MANAGE-4.2 · OWASP:LLM01</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>Third-party PII disclosure (partial)</t>
-  </si>
-  <si>
-    <t>Caught at NLI egress. 0 records released.</t>
-  </si>
-  <si>
-    <t>Internal AI Officer</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>Hallucinated delivery date</t>
-  </si>
-  <si>
-    <t>Flagged by divergence check. Caller notified of error.</t>
-  </si>
-  <si>
-    <t>5.2 — Severity Distribution</t>
-  </si>
-  <si>
-    <t>Severity Level</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Avg Estimated Cost</t>
-  </si>
-  <si>
-    <t>SEV-1 Critical</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>SEV-2 Major</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>SEV-3 Moderate</t>
-  </si>
-  <si>
-    <t>44.4%</t>
-  </si>
-  <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>SEV-4 Minor</t>
-  </si>
-  <si>
-    <t>33.3%</t>
-  </si>
-  <si>
-    <t>SEV-5 Info</t>
-  </si>
-  <si>
-    <t>6. TELEMETRY   ·   BASTION-SPECIFIC</t>
-  </si>
-  <si>
-    <t>6.1 — PII Metrics</t>
-  </si>
-  <si>
-    <t>PII Type</t>
-  </si>
-  <si>
-    <t>Detected</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Per-Record Cost ($)</t>
-  </si>
-  <si>
-    <t>Residual Exposure ($)</t>
-  </si>
-  <si>
-    <t>Phone number</t>
-  </si>
-  <si>
-    <t>Physical address</t>
-  </si>
-  <si>
-    <t>Named person (third-party)</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>SSN / SIN</t>
-  </si>
-  <si>
-    <t>Credit card</t>
-  </si>
-  <si>
-    <t>6.2 — Tool Call Metrics</t>
-  </si>
-  <si>
-    <t>Total tool calls attempted</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Blocked by policy</t>
-  </si>
-  <si>
-    <t>Block rate</t>
-  </si>
-  <si>
-    <t>5.56%</t>
-  </si>
-  <si>
-    <t>Top blocked category</t>
-  </si>
-  <si>
-    <t>refund_over_supervisor_threshold</t>
-  </si>
-  <si>
-    <t>Privileged-action threshold violations</t>
-  </si>
-  <si>
-    <t>6.3 — Anomaly &amp; Drift</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>Anomaly rate (novel tool patterns)</t>
-  </si>
-  <si>
-    <t>Within bounds</t>
-  </si>
-  <si>
-    <t>Rate anomalies (burst detection)</t>
-  </si>
-  <si>
-    <t>3 / 15s</t>
-  </si>
-  <si>
-    <t>Clean</t>
-  </si>
-  <si>
-    <t>Novel tool alerts</t>
-  </si>
-  <si>
-    <t>5 / week</t>
-  </si>
-  <si>
-    <t>Consistency score (hallucination rate)</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>&lt; 0.8 alerts</t>
-  </si>
-  <si>
-    <t>Behavior change detection</t>
-  </si>
-  <si>
-    <t>nominal</t>
-  </si>
-  <si>
-    <t>conservative / fail-closed</t>
-  </si>
-  <si>
-    <t>Nominal</t>
-  </si>
-  <si>
-    <t>7. FRAMEWORK MAP   ·   BASTION-SPECIFIC</t>
-  </si>
-  <si>
-    <t>7.1 — Detection × Framework Matrix</t>
-  </si>
-  <si>
-    <t>Every Bastion detection type carries simultaneous tags for NIST AI RMF, OWASP LLM Top 10, ISO/IEC 42001, EU AI Act, and MITRE ATLAS. This is the matrix underwriters price against.</t>
-  </si>
-  <si>
-    <t>Bastion Detection</t>
-  </si>
-  <si>
-    <t>NIST AI RMF 1.0</t>
-  </si>
-  <si>
-    <t>OWASP LLM Top 10</t>
-  </si>
-  <si>
-    <t>ISO/IEC 42001</t>
-  </si>
-  <si>
-    <t>EU AI Act</t>
-  </si>
-  <si>
-    <t>MITRE ATLAS</t>
-  </si>
-  <si>
-    <t>MEASURE-2.10, MANAGE-4.3</t>
-  </si>
-  <si>
-    <t>LLM06</t>
-  </si>
-  <si>
-    <t>A.6.1.5, A.6.2.7</t>
-  </si>
-  <si>
-    <t>Art. 10, Art. 13</t>
-  </si>
-  <si>
-    <t>AML.T0051</t>
-  </si>
-  <si>
-    <t>MEASURE-2.10, MEASURE-2.3</t>
-  </si>
-  <si>
-    <t>A.6.1.5</t>
-  </si>
-  <si>
-    <t>Art. 10</t>
-  </si>
-  <si>
-    <t>AML.T0024</t>
-  </si>
-  <si>
-    <t>divergence (hallucination)</t>
-  </si>
-  <si>
-    <t>MEASURE-2.3, MEASURE-2.8</t>
-  </si>
-  <si>
-    <t>LLM09</t>
-  </si>
-  <si>
-    <t>A.6.2.4</t>
-  </si>
-  <si>
-    <t>Art. 15</t>
-  </si>
-  <si>
-    <t>AML.T0043</t>
-  </si>
-  <si>
-    <t>canary_disclosure (prompt / tool leak)</t>
-  </si>
-  <si>
-    <t>MEASURE-2.7, MANAGE-2.3</t>
-  </si>
-  <si>
-    <t>LLM01, LLM02</t>
-  </si>
-  <si>
-    <t>A.6.2.7, A.6.2.8</t>
-  </si>
-  <si>
-    <t>Art. 15 (cyber)</t>
-  </si>
-  <si>
-    <t>AML.T0054</t>
-  </si>
-  <si>
-    <t>policy_violation (excessive agency)</t>
-  </si>
-  <si>
-    <t>MANAGE-4.2, GOVERN-3.2</t>
-  </si>
-  <si>
-    <t>LLM08</t>
-  </si>
-  <si>
-    <t>A.6.1.2, A.6.2.1</t>
-  </si>
-  <si>
-    <t>Art. 14 (oversight)</t>
-  </si>
-  <si>
-    <t>AML.T0053</t>
-  </si>
-  <si>
-    <t>behavior change detection</t>
-  </si>
-  <si>
-    <t>MEASURE-3.2, MEASURE-4.1</t>
-  </si>
-  <si>
-    <t>A.6.2.5</t>
-  </si>
-  <si>
-    <t>Art. 15 (accuracy)</t>
-  </si>
-  <si>
-    <t>AML.T0034</t>
-  </si>
-  <si>
-    <t>red-team finding (adversarial)</t>
-  </si>
-  <si>
-    <t>MANAGE-4.1, MAP-5.1</t>
-  </si>
-  <si>
-    <t>A.6.2.6</t>
-  </si>
-  <si>
-    <t>Art. 15, Annex IV</t>
-  </si>
-  <si>
-    <t>Per-finding ATLAS ID</t>
-  </si>
-  <si>
-    <t>7.2 — Framework Coverage Summary</t>
-  </si>
-  <si>
-    <t>Framework</t>
-  </si>
-  <si>
-    <t>Controls Tagged</t>
-  </si>
-  <si>
-    <t>Coverage %</t>
-  </si>
-  <si>
-    <t>NIST AI RMF</t>
-  </si>
-  <si>
-    <t>1.0 (Jan 2023)</t>
-  </si>
-  <si>
-    <t>9 categories (GOVERN, MAP, MEASURE, MANAGE)</t>
-  </si>
-  <si>
-    <t>86%</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>10 / 10</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>9 controls in A.6.x</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>final 2024</t>
-  </si>
-  <si>
-    <t>Art. 10, 13, 14, 15 + Annex IV</t>
-  </si>
-  <si>
-    <t>71%</t>
-  </si>
-  <si>
-    <t>2025.1</t>
-  </si>
-  <si>
-    <t>7 tactics / 14 techniques</t>
-  </si>
-  <si>
-    <t>92%</t>
-  </si>
-  <si>
-    <t>8. ATTESTATION</t>
-  </si>
-  <si>
-    <t>8.1 — Controls In Place</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>Last Verified</t>
-  </si>
-  <si>
-    <t>AI reviewer evaluates every agent reply</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Groundedness + Authorization</t>
-  </si>
-  <si>
     <t>Knowledge graph of policies and tools</t>
   </si>
   <si>
@@ -1350,7 +1347,7 @@
     <t>All telemetry sourced from Bastion Blue proxy at the point of interception. Events are tamper-evident with sequential IDs + daily Merkle roots. No manual adjustments.</t>
   </si>
   <si>
-    <t>Risk scores use the weighted component model: PII (30%), Policy (25%), Anomaly (20%), Integrity (15%), Drift (10%). Financial exposure uses IBM/Ponemon 2025 $180/record benchmark. Severity follows NIST IR framework adapted for AI failure modes.</t>
+    <t>Risk scores use the weighted component model: PII (30%), Policy (25%), Anomaly (20%), Integrity (15%), Drift (10%). Per-line-item contributions are weight × event count, normalised against a 100-point ceiling. Severity follows NIST IR framework adapted for AI failure modes.</t>
   </si>
   <si>
     <t>Compliance alignment</t>
@@ -2055,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2326,23 +2323,7 @@
         <v>85</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2350,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2391,7 +2372,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2399,7 +2380,7 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2407,28 +2388,28 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>5</v>
@@ -2436,28 +2417,28 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>106</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>64</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>47</v>
@@ -2465,19 +2446,19 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>63</v>
@@ -2486,27 +2467,27 @@
         <v>63</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>117</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>63</v>
@@ -2515,27 +2496,27 @@
         <v>63</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>64</v>
@@ -2544,7 +2525,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>47</v>
@@ -2552,19 +2533,19 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>64</v>
@@ -2573,27 +2554,27 @@
         <v>64</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="E13" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>63</v>
@@ -2602,7 +2583,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>47</v>
@@ -2610,7 +2591,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -2618,79 +2599,79 @@
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2718,7 +2699,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2740,7 +2721,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -2748,7 +2729,7 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2756,49 +2737,49 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>49</v>
@@ -2812,7 +2793,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2820,7 +2801,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2828,117 +2809,117 @@
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="E17" s="12" t="s">
         <v>177</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>181</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="E20" s="12" t="s">
         <v>191</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
     </row>
-    <row r="24" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2946,122 +2927,122 @@
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="F25" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>206</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" s="12" t="s">
         <v>214</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3092,7 +3073,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3114,7 +3095,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3122,7 +3103,7 @@
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3130,237 +3111,237 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>221</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="E8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>228</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="E10" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>238</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="E12" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -3368,36 +3349,36 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>63</v>
@@ -3406,7 +3387,7 @@
         <v>63</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>54</v>
@@ -3414,10 +3395,10 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>64</v>
@@ -3429,15 +3410,15 @@
         <v>63</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>64</v>
@@ -3452,7 +3433,7 @@
         <v>63</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>54</v>
@@ -3460,22 +3441,22 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>54</v>
@@ -3483,10 +3464,10 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>63</v>
@@ -3495,13 +3476,13 @@
         <v>63</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3529,7 +3510,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3551,7 +3532,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3559,7 +3540,7 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3567,99 +3548,99 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>278</v>
-      </c>
       <c r="G7" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>280</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>47</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -3667,86 +3648,86 @@
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>207</v>
+        <v>293</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>205</v>
+        <v>295</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="D18" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>207</v>
+        <v>295</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3755,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3796,7 +3777,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -3804,47 +3785,47 @@
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>207</v>
+      <c r="E7" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>64</v>
@@ -3855,16 +3836,16 @@
       <c r="D8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>207</v>
+      <c r="E8" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>64</v>
@@ -3875,16 +3856,16 @@
       <c r="D9" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>207</v>
+      <c r="E9" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>63</v>
@@ -3895,16 +3876,16 @@
       <c r="D10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>207</v>
+      <c r="E10" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>63</v>
@@ -3915,16 +3896,16 @@
       <c r="D11" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>207</v>
+      <c r="E11" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>63</v>
@@ -3935,36 +3916,36 @@
       <c r="D12" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>207</v>
+      <c r="E12" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>207</v>
+      <c r="E13" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -3980,55 +3961,55 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -4036,13 +4017,13 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>39</v>
@@ -4050,72 +4031,72 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>73</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>341</v>
-      </c>
       <c r="D31" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="D32" s="12" t="s">
         <v>343</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -4143,7 +4124,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4165,7 +4146,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -4173,7 +4154,7 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -4181,167 +4162,167 @@
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>357</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>361</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>367</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="E11" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>373</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>379</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>384</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>389</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -4349,86 +4330,86 @@
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>397</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B21" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>402</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>405</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>408</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4455,7 +4436,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4477,7 +4458,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -4485,147 +4466,147 @@
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>417</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="C12" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>428</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>431</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="D14" s="12" t="s">
         <v>435</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -4633,18 +4614,18 @@
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>439</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="20" ht="70" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>441</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="21" ht="70" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4652,39 +4633,39 @@
         <v>15</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" ht="70" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>444</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="23" ht="70" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>446</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="24" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>448</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>450</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>451</v>
       </c>
     </row>
   </sheetData>
